--- a/BioTern/assets/Internal Students Template.xlsx
+++ b/BioTern/assets/Internal Students Template.xlsx
@@ -20,20 +20,41 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -42,7 +63,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -52,13 +75,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="12" width="18" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="48" customWidth="1"/>
+    <col min="7" max="7" width="72" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="38" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
           <t>student_no</t>
@@ -66,61 +99,56 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t>user_id</t>
+          <t>school_year</t>
         </is>
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t>last_name</t>
+          <t>STUDENT NAME</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
-          <t>first_name</t>
+          <t>CONTACT NO.</t>
         </is>
       </c>
       <c r="E1" t="inlineStr" s="1">
         <is>
-          <t>middle_name</t>
+          <t>SECTION</t>
         </is>
       </c>
       <c r="F1" t="inlineStr" s="1">
         <is>
-          <t>course_id</t>
+          <t>COMPANY</t>
         </is>
       </c>
       <c r="G1" t="inlineStr" s="1">
         <is>
-          <t>section_id</t>
+          <t>ADDRESS</t>
         </is>
       </c>
       <c r="H1" t="inlineStr" s="1">
         <is>
-          <t>email</t>
+          <t>SUPERVISOR NAME</t>
         </is>
       </c>
       <c r="I1" t="inlineStr" s="1">
         <is>
-          <t>password</t>
+          <t>POSITION</t>
         </is>
       </c>
       <c r="J1" t="inlineStr" s="1">
         <is>
-          <t>status</t>
+          <t>COMPANY REPRESENTATIVE</t>
         </is>
       </c>
       <c r="K1" t="inlineStr" s="1">
         <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr" s="1">
-        <is>
-          <t>update_at</t>
+          <t>STATUS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:K1"/>
 </worksheet>
 </file>
--- a/BioTern/assets/Internal Students Template.xlsx
+++ b/BioTern/assets/Internal Students Template.xlsx
@@ -1,13 +1,20 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheets>
-    <sheet name="Internal Students" sheetId="1" r:id="rId1"/>
-  </sheets>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>BioTern</Application>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>BioTern</dc:creator>
+  <cp:lastModifiedBy>BioTern</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-05-01T00:00:00Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-05-01T00:00:00Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
@@ -73,22 +80,27 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Internal Students" sheetId="1" r:id="rId1"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="48" customWidth="1"/>
-    <col min="7" max="7" width="72" customWidth="1"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="38" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -99,56 +111,41 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t>school_year</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t>STUDENT NAME</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
-          <t>CONTACT NO.</t>
+          <t>middle_name</t>
         </is>
       </c>
       <c r="E1" t="inlineStr" s="1">
         <is>
-          <t>SECTION</t>
+          <t>email</t>
         </is>
       </c>
       <c r="F1" t="inlineStr" s="1">
         <is>
-          <t>COMPANY</t>
+          <t>course_id</t>
         </is>
       </c>
       <c r="G1" t="inlineStr" s="1">
         <is>
-          <t>ADDRESS</t>
+          <t>section_id</t>
         </is>
       </c>
       <c r="H1" t="inlineStr" s="1">
         <is>
-          <t>SUPERVISOR NAME</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr" s="1">
-        <is>
-          <t>POSITION</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr" s="1">
-        <is>
-          <t>COMPANY REPRESENTATIVE</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr" s="1">
-        <is>
-          <t>STATUS</t>
+          <t>password</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:H1"/>
 </worksheet>
 </file>
--- a/BioTern/assets/Internal Students Template.xlsx
+++ b/BioTern/assets/Internal Students Template.xlsx
@@ -1,20 +1,13 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>BioTern</Application>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Internal Students" sheetId="1" r:id="rId1"/>
+  </sheets>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:creator>BioTern</dc:creator>
-  <cp:lastModifiedBy>BioTern</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-05-01T00:00:00Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-05-01T00:00:00Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
@@ -27,41 +20,20 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -70,9 +42,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -80,30 +50,22 @@
 </styleSheet>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheets>
-    <sheet name="Internal Students" sheetId="1" r:id="rId1"/>
-  </sheets>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="46" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
           <t>student_no</t>
